--- a/src/workbook/IRRBB_Template.xlsx
+++ b/src/workbook/IRRBB_Template.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="116">
   <si>
     <t xml:space="preserve">IRRBB Toolkit</t>
   </si>

--- a/src/workbook/IRRBB_Template.xlsx
+++ b/src/workbook/IRRBB_Template.xlsx
@@ -29,7 +29,12 @@
     <definedName name="Config_RatesFile">Config!$B$7</definedName>
     <definedName name="Config_WindowEnd">Config!$B$9</definedName>
     <definedName name="Config_WindowStart">Config!$B$8</definedName>
+    <definedName name="DataSummary_Findings">DataSummary!$G$14:$J$20013</definedName>
+    <definedName name="DataSummary_Info">DataSummary!$B$4:$B$12</definedName>
+    <definedName name="DataSummary_Lineage">DataSummary!$P$14:$Q$63</definedName>
     <definedName name="DataSummary_Status">DataSummary!$B$3</definedName>
+    <definedName name="DataSummary_Totals">DataSummary!$A$14:$E$20013</definedName>
+    <definedName name="DataSummary_Warnings">DataSummary!$L$14:$N$20013</definedName>
     <definedName name="ModelParams_Status">ModelParams!$B$3</definedName>
     <definedName name="Results_Status">Results!$B$3</definedName>
     <definedName name="Scenarios_Status">Scenarios!$B$3</definedName>
@@ -41,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="128">
   <si>
     <t xml:space="preserve">IRRBB Toolkit</t>
   </si>
@@ -145,7 +150,7 @@
     <t xml:space="preserve">VBA</t>
   </si>
   <si>
-    <t xml:space="preserve">Placeholder: import summary and lineage (v0.2.0, not built)</t>
+    <t xml:space="preserve">Implemented: import totals, findings, warnings and lineage (#71; lineage fingerprint pending)</t>
   </si>
   <si>
     <t xml:space="preserve">ModelParams</t>
@@ -313,15 +318,63 @@
     <t xml:space="preserve">NOT RUN - not implemented</t>
   </si>
   <si>
+    <t xml:space="preserve">Started</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finished</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market-rate file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data window</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closures attested</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cleanup error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Currency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accounts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model parameters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Versioned parameter sets of the decay, rate and stable-amount models.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reserved: no function writes this sheet yet. The result layout from row 13 is defined when the function is built (docs/WORKBOOK_CONTRACT.md).</t>
   </si>
   <si>
-    <t xml:space="preserve">Model parameters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Versioned parameter sets of the decay, rate and stable-amount models.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Estimation results and diagnostics of each model.</t>
   </si>
   <si>
@@ -340,12 +393,6 @@
     <t xml:space="preserve">NOT RUN</t>
   </si>
   <si>
-    <t xml:space="preserve">Started</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finished</t>
-  </si>
-  <si>
     <t xml:space="preserve">Host</t>
   </si>
   <si>
@@ -353,12 +400,6 @@
   </si>
   <si>
     <t xml:space="preserve">Assertions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cleanup error</t>
   </si>
   <si>
     <t xml:space="preserve">Case</t>
@@ -830,7 +871,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3">
@@ -838,18 +879,18 @@
         <v>18</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B4" s="8"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B5" s="8"/>
     </row>
@@ -861,73 +902,73 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="B7" s="7"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="B8" s="7"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="B9" s="7"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="B10" s="7"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B11" s="7"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1166,11 +1207,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="shDataSummary"/>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="3" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="8" customWidth="1"/>
+    <col min="9" max="9" width="7" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="3" customWidth="1"/>
+    <col min="12" max="12" width="7" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="15" width="3" customWidth="1"/>
+    <col min="16" max="16" width="30" customWidth="1"/>
+    <col min="17" max="17" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1191,9 +1247,102 @@
         <v>89</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="8"/>
+    </row>
     <row r="5">
-      <c r="A5" s="9" t="s">
-        <v>90</v>
+      <c r="A5" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="8"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="7"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="7"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B8" s="7"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="7"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" s="7"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" s="7"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="7"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="P13" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1224,12 +1373,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3">
@@ -1242,7 +1391,7 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1278,7 +1427,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3">
@@ -1291,7 +1440,7 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1327,7 +1476,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3">
@@ -1340,7 +1489,7 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1376,7 +1525,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3">
@@ -1389,7 +1538,7 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1425,7 +1574,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3">
@@ -1438,7 +1587,7 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/src/workbook/IRRBB_Template.xlsx
+++ b/src/workbook/IRRBB_Template.xlsx
@@ -36,6 +36,7 @@
     <definedName name="DataSummary_Totals">DataSummary!$A$14:$E$20013</definedName>
     <definedName name="DataSummary_Warnings">DataSummary!$L$14:$N$20013</definedName>
     <definedName name="ModelParams_Status">ModelParams!$B$3</definedName>
+    <definedName name="Readme_SourceCommit">Readme!$B$5</definedName>
     <definedName name="Results_Status">Results!$B$3</definedName>
     <definedName name="Scenarios_Status">Scenarios!$B$3</definedName>
     <definedName name="Segments_Codes">Segments!$A$6:$A$8</definedName>
@@ -150,7 +151,7 @@
     <t xml:space="preserve">VBA</t>
   </si>
   <si>
-    <t xml:space="preserve">Implemented: import totals, findings, warnings and lineage (#71; lineage fingerprint pending)</t>
+    <t xml:space="preserve">Implemented: import totals, findings, warnings and lineage (#71)</t>
   </si>
   <si>
     <t xml:space="preserve">ModelParams</t>

--- a/src/workbook/IRRBB_Template.xlsx
+++ b/src/workbook/IRRBB_Template.xlsx
@@ -32,6 +32,7 @@
     <definedName name="DataSummary_Findings">DataSummary!$G$14:$J$20013</definedName>
     <definedName name="DataSummary_Info">DataSummary!$B$4:$B$12</definedName>
     <definedName name="DataSummary_Lineage">DataSummary!$P$14:$Q$63</definedName>
+    <definedName name="DataSummary_Outcomes">DataSummary!$S$14:$AB$20013</definedName>
     <definedName name="DataSummary_Status">DataSummary!$B$3</definedName>
     <definedName name="DataSummary_Totals">DataSummary!$A$14:$E$20013</definedName>
     <definedName name="DataSummary_Warnings">DataSummary!$L$14:$N$20013</definedName>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="135">
   <si>
     <t xml:space="preserve">IRRBB Toolkit</t>
   </si>
@@ -151,7 +152,7 @@
     <t xml:space="preserve">VBA</t>
   </si>
   <si>
-    <t xml:space="preserve">Implemented: import totals, findings, warnings and lineage (#71)</t>
+    <t xml:space="preserve">Implemented: import totals, outcomes, findings, warnings and lineage (#71)</t>
   </si>
   <si>
     <t xml:space="preserve">ModelParams</t>
@@ -365,6 +366,27 @@
   </si>
   <si>
     <t xml:space="preserve">Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verified closures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gaps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Censored</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Censored last balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End of sample</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Close dates masked</t>
   </si>
   <si>
     <t xml:space="preserve">Model parameters</t>
@@ -872,7 +894,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3">
@@ -880,7 +902,7 @@
         <v>18</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4">
@@ -903,19 +925,19 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B7" s="7"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B8" s="7"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B9" s="7"/>
     </row>
@@ -933,43 +955,43 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="L13" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="N13" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="N13" s="4" t="s">
-        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1208,7 +1230,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="shDataSummary"/>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:AB13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1228,6 +1250,17 @@
     <col min="15" max="15" width="3" customWidth="1"/>
     <col min="16" max="16" width="30" customWidth="1"/>
     <col min="17" max="17" width="22" customWidth="1"/>
+    <col min="18" max="18" width="3" customWidth="1"/>
+    <col min="19" max="19" width="12" customWidth="1"/>
+    <col min="20" max="20" width="10" customWidth="1"/>
+    <col min="21" max="21" width="9" customWidth="1"/>
+    <col min="22" max="22" width="10" customWidth="1"/>
+    <col min="23" max="23" width="16" customWidth="1"/>
+    <col min="24" max="24" width="7" customWidth="1"/>
+    <col min="25" max="25" width="9" customWidth="1"/>
+    <col min="26" max="26" width="20" customWidth="1"/>
+    <col min="27" max="27" width="13" customWidth="1"/>
+    <col min="28" max="28" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1344,6 +1377,36 @@
       </c>
       <c r="Q13" s="4" t="s">
         <v>57</v>
+      </c>
+      <c r="S13" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="T13" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="U13" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="V13" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="W13" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="X13" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y13" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z13" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA13" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB13" s="4" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -1374,12 +1437,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3">
@@ -1392,7 +1455,7 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1428,7 +1491,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3">
@@ -1441,7 +1504,7 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1477,7 +1540,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3">
@@ -1490,7 +1553,7 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1526,7 +1589,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3">
@@ -1539,7 +1602,7 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1575,7 +1638,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3">
@@ -1588,7 +1651,7 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/src/workbook/IRRBB_Template.xlsx
+++ b/src/workbook/IRRBB_Template.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="136">
   <si>
     <t xml:space="preserve">IRRBB Toolkit</t>
   </si>
@@ -131,13 +131,16 @@
     <t xml:space="preserve">User</t>
   </si>
   <si>
-    <t xml:space="preserve">Input area defined; read by the data importer (v0.2.0, not built)</t>
+    <t xml:space="preserve">Implemented: run settings read by the data importer (#71)</t>
   </si>
   <si>
     <t xml:space="preserve">Segments</t>
   </si>
   <si>
     <t xml:space="preserve">shSegments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implemented: segment selection read by the data importer (#71)</t>
   </si>
   <si>
     <t xml:space="preserve">DataSummary</t>
@@ -733,131 +736,131 @@
         <v>26</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -889,12 +892,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3">
@@ -902,18 +905,18 @@
         <v>18</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B4" s="8"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B5" s="8"/>
     </row>
@@ -925,73 +928,73 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B7" s="7"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B8" s="7"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B9" s="7"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B10" s="7"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B11" s="7"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="D13" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="I13" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="N13" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="N13" s="4" t="s">
-        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -1044,98 +1047,98 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1170,51 +1173,51 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1265,12 +1268,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
@@ -1278,135 +1281,135 @@
         <v>18</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B4" s="8"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B5" s="8"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B6" s="7"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B7" s="7"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B8" s="7"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B9" s="7"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B10" s="7"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B11" s="7"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B12" s="7"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="J13" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="L13" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="P13" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="S13" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="T13" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="U13" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="N13" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="P13" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q13" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S13" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="T13" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="U13" s="4" t="s">
-        <v>99</v>
-      </c>
       <c r="V13" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="W13" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="X13" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y13" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Z13" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA13" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AB13" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -1437,12 +1440,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3">
@@ -1450,12 +1453,12 @@
         <v>18</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1486,12 +1489,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3">
@@ -1499,12 +1502,12 @@
         <v>18</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1535,12 +1538,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3">
@@ -1548,12 +1551,12 @@
         <v>18</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1584,12 +1587,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3">
@@ -1597,12 +1600,12 @@
         <v>18</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1633,12 +1636,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3">
@@ -1646,12 +1649,12 @@
         <v>18</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/src/workbook/IRRBB_Template.xlsx
+++ b/src/workbook/IRRBB_Template.xlsx
@@ -42,21 +42,37 @@
     <definedName name="Scenarios_Status">Scenarios!$B$3</definedName>
     <definedName name="Segments_Codes">Segments!$A$6:$A$8</definedName>
     <definedName name="Segments_Include">Segments!$C$6:$C$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Readme'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Readme'!$A$1:$E$33</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Config'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Config'!$A$1:$D$23</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Segments'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Segments'!$A$1:$C$11</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'DataSummary'!$1:$13</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'ModelParams'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Calibration'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Backtesting'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Scenarios'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Results'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Checks'!$1:$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="155">
+  <si>
+    <t xml:space="preserve">K-IRRBB</t>
+  </si>
   <si>
     <t xml:space="preserve">IRRBB Toolkit</t>
   </si>
   <si>
-    <t xml:space="preserve">Workbook for IRRBB behavioral models. This sheet maps every sheet and records the build.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Build</t>
+    <t xml:space="preserve">Start with Config and Segments. Import data in the development workbook, then review DataSummary. Yellow cells are inputs; blue tabs hold outputs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build information</t>
   </si>
   <si>
     <t xml:space="preserve">Source commit</t>
@@ -89,7 +105,7 @@
     <t xml:space="preserve">Not applicable</t>
   </si>
   <si>
-    <t xml:space="preserve">Sheets</t>
+    <t xml:space="preserve">Workbook map and readiness</t>
   </si>
   <si>
     <t xml:space="preserve">Sheet</t>
@@ -215,6 +231,33 @@
     <t xml:space="preserve">A sheet name is not evidence that a function exists: the Status column says what is implemented. Contract: docs/WORKBOOK_CONTRACT.md.</t>
   </si>
   <si>
+    <t xml:space="preserve">How to use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Configure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On Config, choose the account and rate files, set month-end dates and the rate series, and complete the closure attestation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Select segments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On Segments, choose Yes or No for each segment to include in the run.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Import and review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the development workbook, use Import data on Config. Review the status, totals, findings, warnings and lineage on DataSummary.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Check readiness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run the development workbook's regression tests on Checks. Reserved model sheets remain unavailable until their functions are implemented.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Run settings</t>
   </si>
   <si>
@@ -281,6 +324,9 @@
     <t xml:space="preserve">Closures are reported by the month end in which they occur (DATA_CONTRACT.md). No: the import stops.</t>
   </si>
   <si>
+    <t xml:space="preserve">Yellow cells identify inputs. File paths are selected with the buttons in the development workbook; the macro-free template has no action buttons.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Segments of the data contract; choose which ones a run includes.</t>
   </si>
   <si>
@@ -314,15 +360,18 @@
     <t xml:space="preserve">Wholesale, non-financial corporate</t>
   </si>
   <si>
+    <t xml:space="preserve">Yellow cells are editable. Choose Yes to include a segment, or No to leave it out.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Data summary</t>
   </si>
   <si>
+    <t xml:space="preserve">NOT RUN - not implemented</t>
+  </si>
+  <si>
     <t xml:space="preserve">Import counts, reconciliation, warnings and lineage of the loaded data.</t>
   </si>
   <si>
-    <t xml:space="preserve">NOT RUN - not implemented</t>
-  </si>
-  <si>
     <t xml:space="preserve">Started</t>
   </si>
   <si>
@@ -344,6 +393,21 @@
     <t xml:space="preserve">Cleanup error</t>
   </si>
   <si>
+    <t xml:space="preserve">Monthly totals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Findings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warnings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source lineage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly outcomes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Date</t>
   </si>
   <si>
@@ -413,12 +477,12 @@
     <t xml:space="preserve">Results of the latest run for review and export.</t>
   </si>
   <si>
+    <t xml:space="preserve">NOT RUN</t>
+  </si>
+  <si>
     <t xml:space="preserve">Regression harness (TEST_Harness.RunTests) output: run status, cases and assertions.</t>
   </si>
   <si>
-    <t xml:space="preserve">NOT RUN</t>
-  </si>
-  <si>
     <t xml:space="preserve">Host</t>
   </si>
   <si>
@@ -426,6 +490,12 @@
   </si>
   <si>
     <t xml:space="preserve">Assertions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test cases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assertion detail</t>
   </si>
   <si>
     <t xml:space="preserve">Case</t>
@@ -462,45 +532,67 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="0.00E+00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="8">
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="14"/>
-      <color rgb="FF1F3A5F"/>
-      <name val="Calibri"/>
+      <sz val="18"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
       <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="11"/>
-      <color rgb="FF5B6573"/>
-      <name val="Calibri"/>
+      <sz val="10"/>
+      <color rgb="FF595959"/>
+      <name val="Aptos"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFFC000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F3864"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Aptos"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -509,13 +601,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F3A5F"/>
+        <fgColor rgb="FF1F3864"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F4F7"/>
+        <fgColor rgb="FFF7F7F7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -525,8 +617,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF000000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF265A99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E75B6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -536,16 +646,25 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFC8CED6"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="FFC8CED6"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="FFC8CED6"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFC8CED6"/>
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF1F3864"/>
       </bottom>
       <diagonal/>
     </border>
@@ -553,20 +672,60 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+  <cellXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="0" indent="0"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="0" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="0" indent="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="0" indent="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="0" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="0" indent="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="0" indent="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="0" indent="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="0" indent="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -574,6 +733,9 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
@@ -581,6 +743,9 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
@@ -588,6 +753,9 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
@@ -600,404 +768,489 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr codeName="shReadme"/>
-  <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr codeName="shReadme">
+    <tabColor rgb="FF1F3864"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr defaultRowHeight="22"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="72" customWidth="1"/>
+    <col min="1" max="1" width="23" customWidth="1" style="0"/>
+    <col min="2" max="2" width="30" customWidth="1" style="0"/>
+    <col min="3" max="3" width="16" customWidth="1" style="0"/>
+    <col min="4" max="4" width="12" customWidth="1" style="0"/>
+    <col min="5" max="5" width="64" customWidth="1" style="0"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="2" ht="27" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5">
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>7</v>
-      </c>
       <c r="E13" s="9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="D15" s="9" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>26</v>
-      </c>
       <c r="E15" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
       <c r="A16" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D16" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="D17" s="9" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="9" t="s">
+      <c r="E17" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E17" s="9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>33</v>
-      </c>
       <c r="D18" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E18" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>33</v>
-      </c>
       <c r="D19" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E19" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>33</v>
-      </c>
       <c r="D20" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>33</v>
-      </c>
       <c r="D21" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>33</v>
-      </c>
       <c r="D22" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
       <c r="A24" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <mergeCells count="16">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+  </mergeCells>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr codeName="shChecks"/>
+  <sheetPr codeName="shChecks">
+    <tabColor rgb="FF548235"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:N13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="22"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="60" customWidth="1"/>
-    <col min="7" max="7" width="3" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="34" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1" style="0"/>
+    <col min="2" max="2" width="40" customWidth="1" style="0"/>
+    <col min="3" max="3" width="11" customWidth="1" style="15"/>
+    <col min="4" max="4" width="9" customWidth="1" style="15"/>
+    <col min="5" max="5" width="9" customWidth="1" style="15"/>
+    <col min="6" max="6" width="60" customWidth="1" style="0"/>
+    <col min="7" max="7" width="3" customWidth="1" style="0"/>
+    <col min="8" max="8" width="14" customWidth="1" style="0"/>
+    <col min="9" max="9" width="34" customWidth="1" style="0"/>
+    <col min="10" max="10" width="18" customWidth="1" style="0"/>
+    <col min="11" max="11" width="18" customWidth="1" style="0"/>
+    <col min="12" max="12" width="10" customWidth="1" style="16"/>
+    <col min="13" max="13" width="14" customWidth="1" style="16"/>
+    <col min="14" max="14" width="9" customWidth="1" style="0"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="3">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" ht="27" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>138</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="B4" s="8"/>
     </row>
-    <row r="5">
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="B5" s="8"/>
     </row>
-    <row r="6">
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" s="7"/>
     </row>
-    <row r="7">
+    <row r="7" ht="24" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="B7" s="7"/>
     </row>
-    <row r="8">
+    <row r="8" ht="24" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="B8" s="7"/>
     </row>
-    <row r="9">
+    <row r="9" ht="24" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="B9" s="7"/>
     </row>
-    <row r="10">
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="B10" s="7"/>
     </row>
-    <row r="11">
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B11" s="7"/>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="N13" s="4" t="s">
-        <v>127</v>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="N13" s="11" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="D3:N4"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="H12:N12"/>
+  </mergeCells>
   <conditionalFormatting sqref="B3">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>OR(LEFT($B$3,6)="FAILED",$B$3="COMPLETE - FAILURES")</formula>
@@ -1029,119 +1282,140 @@
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="0" fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr codeName="shConfig"/>
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr codeName="shConfig">
+    <tabColor rgb="FFBF9000"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="22"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="90" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1" style="0"/>
+    <col min="2" max="2" width="46" customWidth="1" style="0"/>
+    <col min="3" max="3" width="14" customWidth="1" style="0"/>
+    <col min="4" max="4" width="70" customWidth="1" style="0"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" ht="27" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="9" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="9" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="9" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="9" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="9" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="9" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>76</v>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="13" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A12:D12"/>
+  </mergeCells>
   <dataValidations count="2">
     <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" error="Enter a month-end date from 1900 to 9999." sqref="B8:B9">
       <formula1>1</formula1>
@@ -1151,268 +1425,322 @@
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr codeName="shSegments"/>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr codeName="shSegments">
+    <tabColor rgb="FFBF9000"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="22"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1" style="0"/>
+    <col min="2" max="2" width="52" customWidth="1" style="0"/>
+    <col min="3" max="3" width="14" customWidth="1" style="0"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" ht="27" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="13" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1"/>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A10:C11"/>
+  </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="Choose Yes or No." sqref="C6:C8">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr codeName="shDataSummary"/>
+  <sheetPr codeName="shDataSummary">
+    <tabColor rgb="FF2E75B6"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:AB13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="22"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="3" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="9" width="7" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="3" customWidth="1"/>
-    <col min="12" max="12" width="7" customWidth="1"/>
-    <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="3" customWidth="1"/>
-    <col min="16" max="16" width="30" customWidth="1"/>
-    <col min="17" max="17" width="22" customWidth="1"/>
-    <col min="18" max="18" width="3" customWidth="1"/>
-    <col min="19" max="19" width="12" customWidth="1"/>
-    <col min="20" max="20" width="10" customWidth="1"/>
-    <col min="21" max="21" width="9" customWidth="1"/>
-    <col min="22" max="22" width="10" customWidth="1"/>
-    <col min="23" max="23" width="16" customWidth="1"/>
-    <col min="24" max="24" width="7" customWidth="1"/>
-    <col min="25" max="25" width="9" customWidth="1"/>
-    <col min="26" max="26" width="20" customWidth="1"/>
-    <col min="27" max="27" width="13" customWidth="1"/>
-    <col min="28" max="28" width="18" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1" style="17"/>
+    <col min="2" max="2" width="40" customWidth="1" style="0"/>
+    <col min="3" max="3" width="10" customWidth="1" style="0"/>
+    <col min="4" max="4" width="10" customWidth="1" style="15"/>
+    <col min="5" max="5" width="16" customWidth="1" style="14"/>
+    <col min="6" max="6" width="3" customWidth="1" style="0"/>
+    <col min="7" max="7" width="22" customWidth="1" style="0"/>
+    <col min="8" max="8" width="8" customWidth="1" style="15"/>
+    <col min="9" max="9" width="7" customWidth="1" style="0"/>
+    <col min="10" max="10" width="12" customWidth="1" style="17"/>
+    <col min="11" max="11" width="3" customWidth="1" style="0"/>
+    <col min="12" max="12" width="7" customWidth="1" style="0"/>
+    <col min="13" max="13" width="14" customWidth="1" style="0"/>
+    <col min="14" max="14" width="12" customWidth="1" style="17"/>
+    <col min="15" max="15" width="3" customWidth="1" style="0"/>
+    <col min="16" max="16" width="30" customWidth="1" style="0"/>
+    <col min="17" max="17" width="22" customWidth="1" style="0"/>
+    <col min="18" max="18" width="3" customWidth="1" style="0"/>
+    <col min="19" max="19" width="12" customWidth="1" style="17"/>
+    <col min="20" max="20" width="10" customWidth="1" style="0"/>
+    <col min="21" max="21" width="9" customWidth="1" style="0"/>
+    <col min="22" max="22" width="10" customWidth="1" style="15"/>
+    <col min="23" max="23" width="16" customWidth="1" style="15"/>
+    <col min="24" max="24" width="7" customWidth="1" style="15"/>
+    <col min="25" max="25" width="9" customWidth="1" style="15"/>
+    <col min="26" max="26" width="20" customWidth="1" style="14"/>
+    <col min="27" max="27" width="13" customWidth="1" style="15"/>
+    <col min="28" max="28" width="18" customWidth="1" style="15"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" ht="27" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="8"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="8"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="7"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="7"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" s="7"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="7"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="7"/>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B11" s="7"/>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="P12" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="S12" s="12" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="I13" s="11" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B4" s="8"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B5" s="8"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="7"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B7" s="7"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B8" s="7"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="7"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B10" s="7"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B11" s="7"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B12" s="7"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="N13" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="P13" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q13" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="S13" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="T13" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="U13" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="V13" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="W13" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="X13" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y13" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="Z13" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA13" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="AB13" s="4" t="s">
-        <v>113</v>
+      <c r="J13" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="N13" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="P13" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q13" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="S13" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="T13" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="U13" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="V13" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="W13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="X13" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y13" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA13" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB13" s="11" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="A2:AB2"/>
+    <mergeCell ref="D3:J4"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="G12:J12"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="S12:AB12"/>
+  </mergeCells>
   <conditionalFormatting sqref="B3">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>OR(LEFT($B$3,6)="FAILED",$B$3="COMPLETE - FAILURES")</formula>
@@ -1424,44 +1752,65 @@
       <formula>AND(LEFT($B$3,6)&lt;&gt;"FAILED",LEFT($B$3,8)&lt;&gt;"COMPLETE")</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="0" fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr codeName="shModelParams"/>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr codeName="shModelParams">
+    <tabColor rgb="FF2E75B6"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="22"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1" style="0"/>
+    <col min="2" max="2" width="44" customWidth="1" style="0"/>
+    <col min="3" max="3" width="3" customWidth="1" style="0"/>
+    <col min="4" max="4" width="16" customWidth="1" style="0"/>
+    <col min="5" max="5" width="16" customWidth="1" style="0"/>
+    <col min="6" max="6" width="16" customWidth="1" style="0"/>
+    <col min="7" max="7" width="16" customWidth="1" style="0"/>
+    <col min="8" max="8" width="16" customWidth="1" style="0"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" ht="27" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>101</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="26" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>116</v>
-      </c>
-    </row>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1"/>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="D3:H4"/>
+    <mergeCell ref="A5:H6"/>
+  </mergeCells>
   <conditionalFormatting sqref="B3">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>OR(LEFT($B$3,6)="FAILED",$B$3="COMPLETE - FAILURES")</formula>
@@ -1473,44 +1822,65 @@
       <formula>AND(LEFT($B$3,6)&lt;&gt;"FAILED",LEFT($B$3,8)&lt;&gt;"COMPLETE")</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr codeName="shCalibration"/>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr codeName="shCalibration">
+    <tabColor rgb="FF2E75B6"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="22"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1" style="0"/>
+    <col min="2" max="2" width="44" customWidth="1" style="0"/>
+    <col min="3" max="3" width="3" customWidth="1" style="0"/>
+    <col min="4" max="4" width="16" customWidth="1" style="0"/>
+    <col min="5" max="5" width="16" customWidth="1" style="0"/>
+    <col min="6" max="6" width="16" customWidth="1" style="0"/>
+    <col min="7" max="7" width="16" customWidth="1" style="0"/>
+    <col min="8" max="8" width="16" customWidth="1" style="0"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" ht="27" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>101</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="26" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>116</v>
-      </c>
-    </row>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1"/>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="D3:H4"/>
+    <mergeCell ref="A5:H6"/>
+  </mergeCells>
   <conditionalFormatting sqref="B3">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>OR(LEFT($B$3,6)="FAILED",$B$3="COMPLETE - FAILURES")</formula>
@@ -1522,44 +1892,65 @@
       <formula>AND(LEFT($B$3,6)&lt;&gt;"FAILED",LEFT($B$3,8)&lt;&gt;"COMPLETE")</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr codeName="shBacktesting"/>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr codeName="shBacktesting">
+    <tabColor rgb="FF2E75B6"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="22"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1" style="0"/>
+    <col min="2" max="2" width="44" customWidth="1" style="0"/>
+    <col min="3" max="3" width="3" customWidth="1" style="0"/>
+    <col min="4" max="4" width="16" customWidth="1" style="0"/>
+    <col min="5" max="5" width="16" customWidth="1" style="0"/>
+    <col min="6" max="6" width="16" customWidth="1" style="0"/>
+    <col min="7" max="7" width="16" customWidth="1" style="0"/>
+    <col min="8" max="8" width="16" customWidth="1" style="0"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="3">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" ht="27" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>101</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="26" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>116</v>
-      </c>
-    </row>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1"/>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="D3:H4"/>
+    <mergeCell ref="A5:H6"/>
+  </mergeCells>
   <conditionalFormatting sqref="B3">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>OR(LEFT($B$3,6)="FAILED",$B$3="COMPLETE - FAILURES")</formula>
@@ -1571,44 +1962,65 @@
       <formula>AND(LEFT($B$3,6)&lt;&gt;"FAILED",LEFT($B$3,8)&lt;&gt;"COMPLETE")</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr codeName="shScenarios"/>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr codeName="shScenarios">
+    <tabColor rgb="FF2E75B6"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="22"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1" style="0"/>
+    <col min="2" max="2" width="44" customWidth="1" style="0"/>
+    <col min="3" max="3" width="3" customWidth="1" style="0"/>
+    <col min="4" max="4" width="16" customWidth="1" style="0"/>
+    <col min="5" max="5" width="16" customWidth="1" style="0"/>
+    <col min="6" max="6" width="16" customWidth="1" style="0"/>
+    <col min="7" max="7" width="16" customWidth="1" style="0"/>
+    <col min="8" max="8" width="16" customWidth="1" style="0"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="3">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" ht="27" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>101</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="26" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>116</v>
-      </c>
-    </row>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1"/>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="D3:H4"/>
+    <mergeCell ref="A5:H6"/>
+  </mergeCells>
   <conditionalFormatting sqref="B3">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>OR(LEFT($B$3,6)="FAILED",$B$3="COMPLETE - FAILURES")</formula>
@@ -1620,44 +2032,65 @@
       <formula>AND(LEFT($B$3,6)&lt;&gt;"FAILED",LEFT($B$3,8)&lt;&gt;"COMPLETE")</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr codeName="shResults"/>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr codeName="shResults">
+    <tabColor rgb="FF2E75B6"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="22"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1" style="0"/>
+    <col min="2" max="2" width="44" customWidth="1" style="0"/>
+    <col min="3" max="3" width="3" customWidth="1" style="0"/>
+    <col min="4" max="4" width="16" customWidth="1" style="0"/>
+    <col min="5" max="5" width="16" customWidth="1" style="0"/>
+    <col min="6" max="6" width="16" customWidth="1" style="0"/>
+    <col min="7" max="7" width="16" customWidth="1" style="0"/>
+    <col min="8" max="8" width="16" customWidth="1" style="0"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="3">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" ht="27" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>101</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="26" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>116</v>
-      </c>
-    </row>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1"/>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="D3:H4"/>
+    <mergeCell ref="A5:H6"/>
+  </mergeCells>
   <conditionalFormatting sqref="B3">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>OR(LEFT($B$3,6)="FAILED",$B$3="COMPLETE - FAILURES")</formula>
@@ -1669,6 +2102,7 @@
       <formula>AND(LEFT($B$3,6)&lt;&gt;"FAILED",LEFT($B$3,8)&lt;&gt;"COMPLETE")</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
--- a/src/workbook/IRRBB_Template.xlsx
+++ b/src/workbook/IRRBB_Template.xlsx
@@ -61,12 +61,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="154">
   <si>
     <t xml:space="preserve">K-IRRBB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRRBB Toolkit</t>
   </si>
   <si>
     <t xml:space="preserve">Start with Config and Segments. Import data in the development workbook, then review DataSummary. Yellow cells are inputs; blue tabs hold outputs.</t>
@@ -789,291 +786,291 @@
     </row>
     <row r="2" ht="27" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>4</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>6</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>8</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>10</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>12</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="C13" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="D13" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>22</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="C14" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="D14" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="E14" s="9" t="s">
         <v>27</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="C15" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>30</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="C16" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="D16" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="E16" s="9" t="s">
         <v>35</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="C17" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>38</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="C18" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="9" t="s">
         <v>41</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="C19" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="C20" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="9" t="s">
         <v>47</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="C21" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>50</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="C22" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="9" t="s">
         <v>53</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="9" t="s">
         <v>57</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="9" t="s">
         <v>59</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="9" t="s">
         <v>61</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="9" t="s">
         <v>63</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1132,115 +1129,115 @@
     </row>
     <row r="2" ht="27" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B4" s="8"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="8"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="7"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B7" s="7"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B8" s="7"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B9" s="7"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B10" s="7"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B11" s="7"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="H12" s="12" t="s">
         <v>143</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="C13" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D13" s="11" t="s">
+      <c r="E13" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="F13" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="H13" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="I13" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="J13" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="N13" s="11" t="s">
         <v>145</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="K13" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="L13" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="N13" s="11" t="s">
-        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -1309,104 +1306,104 @@
     </row>
     <row r="2" ht="27" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" ht="10" customHeight="1"/>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>72</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>77</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>82</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>85</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1451,62 +1448,62 @@
     </row>
     <row r="2" ht="27" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" ht="10" customHeight="1"/>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="C6" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>96</v>
-      </c>
       <c r="C7" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>98</v>
-      </c>
       <c r="C8" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1"/>
@@ -1573,161 +1570,161 @@
     </row>
     <row r="2" ht="27" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B4" s="8"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="8"/>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B6" s="7"/>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B7" s="7"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B8" s="7"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B9" s="7"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B10" s="7"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B11" s="7"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="G12" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="L12" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="L12" s="12" t="s">
+      <c r="P12" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="P12" s="12" t="s">
+      <c r="S12" s="12" t="s">
         <v>113</v>
-      </c>
-      <c r="S12" s="12" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="C13" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="D13" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="E13" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="G13" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="H13" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="I13" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="M13" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="I13" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="J13" s="11" t="s">
+      <c r="N13" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="P13" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q13" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="S13" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="T13" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="L13" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="N13" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="P13" s="11" t="s">
+      <c r="U13" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="V13" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="Q13" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="S13" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="T13" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="U13" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="V13" s="11" t="s">
+      <c r="W13" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="W13" s="11" t="s">
+      <c r="X13" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="X13" s="11" t="s">
+      <c r="Y13" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="Y13" s="11" t="s">
+      <c r="Z13" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="Z13" s="11" t="s">
+      <c r="AA13" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="AA13" s="11" t="s">
+      <c r="AB13" s="11" t="s">
         <v>129</v>
-      </c>
-      <c r="AB13" s="11" t="s">
-        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -1783,24 +1780,24 @@
     </row>
     <row r="2" ht="27" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1"/>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1"/>
@@ -1853,24 +1850,24 @@
     </row>
     <row r="2" ht="27" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1"/>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1"/>
@@ -1923,24 +1920,24 @@
     </row>
     <row r="2" ht="27" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1"/>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1"/>
@@ -1993,24 +1990,24 @@
     </row>
     <row r="2" ht="27" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1"/>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1"/>
@@ -2063,24 +2060,24 @@
     </row>
     <row r="2" ht="27" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1"/>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1"/>

--- a/src/workbook/IRRBB_Template.xlsx
+++ b/src/workbook/IRRBB_Template.xlsx
@@ -50,7 +50,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="136">
   <si>
-    <t xml:space="preserve">IRRBB Toolkit</t>
+    <t xml:space="preserve">K-IRRBB</t>
   </si>
   <si>
     <t xml:space="preserve">Workbook for IRRBB behavioral models. This sheet maps every sheet and records the build.</t>

--- a/src/workbook/IRRBB_Template.xlsx
+++ b/src/workbook/IRRBB_Template.xlsx
@@ -363,99 +363,102 @@
     <t xml:space="preserve">Data summary</t>
   </si>
   <si>
+    <t xml:space="preserve">NOT RUN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Import counts, reconciliation, warnings and lineage of the loaded data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Started</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finished</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market-rate file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data window</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closures attested</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cleanup error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly totals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Findings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warnings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source lineage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly outcomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Currency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accounts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verified closures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gaps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Censored</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Censored last balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End of sample</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Close dates masked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model parameters</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOT RUN - not implemented</t>
   </si>
   <si>
-    <t xml:space="preserve">Import counts, reconciliation, warnings and lineage of the loaded data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Started</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finished</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Market-rate file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data window</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closures attested</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cleanup error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monthly totals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Findings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warnings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source lineage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monthly outcomes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Segment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Currency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accounts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Account</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verified closures</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gaps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Censored</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Censored last balance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">End of sample</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Close dates masked</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Model parameters</t>
-  </si>
-  <si>
     <t xml:space="preserve">Versioned parameter sets of the decay, rate and stable-amount models.</t>
   </si>
   <si>
@@ -472,9 +475,6 @@
   </si>
   <si>
     <t xml:space="preserve">Results of the latest run for review and export.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOT RUN</t>
   </si>
   <si>
     <t xml:space="preserve">Regression harness (TEST_Harness.RunTests) output: run status, cases and assertions.</t>
@@ -1137,7 +1137,7 @@
         <v>18</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>138</v>
@@ -1788,16 +1788,16 @@
         <v>18</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1"/>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1"/>
@@ -1858,16 +1858,16 @@
         <v>18</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1"/>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1"/>
@@ -1928,16 +1928,16 @@
         <v>18</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1"/>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1"/>
@@ -1998,16 +1998,16 @@
         <v>18</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1"/>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1"/>
@@ -2068,16 +2068,16 @@
         <v>18</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1"/>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1"/>
